--- a/data/trans_dic/P71_R-Clase-trans_dic.xlsx
+++ b/data/trans_dic/P71_R-Clase-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que llega a fin de mes con dificultad o mucha dificultad</t>
+          <t>Población que llega a fin de mes con dificultad o mucha dificultad (tasa de respuesta: 99,03%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>4,6; 9,47</t>
+          <t>4,63; 9,42</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>11,52; 18,86</t>
+          <t>11,41; 18,55</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>9,31; 16,0</t>
+          <t>9,62; 16,26</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>3,15; 7,18</t>
+          <t>3,17; 7,25</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>9,7; 17,93</t>
+          <t>9,7; 17,48</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>10,59; 19,44</t>
+          <t>10,65; 19,46</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>10,1; 16,99</t>
+          <t>9,79; 16,93</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>2,24; 5,31</t>
+          <t>2,21; 5,17</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>7,31; 11,69</t>
+          <t>7,44; 11,66</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>11,92; 17,92</t>
+          <t>12,25; 17,8</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>10,45; 15,39</t>
+          <t>10,58; 15,17</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>2,99; 5,55</t>
+          <t>3,11; 5,54</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>9,52; 16,56</t>
+          <t>9,35; 16,86</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>10,57; 17,72</t>
+          <t>10,72; 17,74</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>18,16; 26,82</t>
+          <t>18,0; 27,03</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>2,33; 5,81</t>
+          <t>2,17; 5,95</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>15,62; 23,57</t>
+          <t>15,56; 23,84</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>13,39; 22,25</t>
+          <t>13,08; 21,41</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>20,8; 30,73</t>
+          <t>20,89; 30,85</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>4,56; 9,04</t>
+          <t>4,55; 8,96</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>13,47; 18,87</t>
+          <t>13,17; 18,81</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>12,83; 18,33</t>
+          <t>12,8; 18,49</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>20,66; 27,04</t>
+          <t>20,64; 26,92</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>3,87; 6,82</t>
+          <t>3,68; 6,57</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>12,09; 18,09</t>
+          <t>12,22; 18,26</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>30,27; 38,41</t>
+          <t>30,23; 37,89</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>33,03; 41,37</t>
+          <t>33,07; 41,36</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2,97; 14,02</t>
+          <t>3,19; 14,14</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>15,75; 28,96</t>
+          <t>15,61; 28,44</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>23,54; 34,86</t>
+          <t>23,35; 35,13</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>25,93; 41,21</t>
+          <t>26,12; 40,97</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>8,21; 16,15</t>
+          <t>8,42; 16,05</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>13,81; 19,28</t>
+          <t>14,07; 19,6</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>29,25; 35,72</t>
+          <t>29,36; 35,86</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>32,9; 40,97</t>
+          <t>32,63; 40,4</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>3,95; 13,78</t>
+          <t>3,85; 13,29</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>20,26; 25,05</t>
+          <t>20,14; 24,93</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>35,47; 41,44</t>
+          <t>35,49; 41,4</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>35,76; 41,77</t>
+          <t>35,42; 41,41</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>12,94; 18,31</t>
+          <t>12,87; 18,15</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>22,1; 29,14</t>
+          <t>22,34; 29,04</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>32,8; 40,29</t>
+          <t>32,69; 40,17</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>35,29; 42,22</t>
+          <t>35,33; 42,03</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>6,69; 16,39</t>
+          <t>6,58; 16,39</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>21,73; 25,54</t>
+          <t>21,74; 25,57</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>35,47; 39,98</t>
+          <t>35,44; 39,95</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>36,34; 40,88</t>
+          <t>36,25; 40,82</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>9,04; 16,0</t>
+          <t>9,32; 16,09</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>29,06; 38,87</t>
+          <t>28,63; 39,0</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>36,97; 45,87</t>
+          <t>36,88; 45,66</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>43,08; 51,8</t>
+          <t>43,8; 51,63</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>21,09; 29,19</t>
+          <t>20,85; 29,03</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>31,42; 39,4</t>
+          <t>30,99; 39,31</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>37,67; 45,27</t>
+          <t>37,66; 45,19</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>49,61; 57,04</t>
+          <t>49,91; 57,25</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>27,8; 53,82</t>
+          <t>27,84; 52,35</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>31,66; 38,25</t>
+          <t>31,44; 38,1</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>38,58; 44,1</t>
+          <t>38,39; 44,22</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>47,85; 53,42</t>
+          <t>47,93; 53,53</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>26,43; 44,93</t>
+          <t>26,44; 42,81</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>8,38; 16,07</t>
+          <t>8,32; 15,5</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>15,81; 26,09</t>
+          <t>15,96; 25,18</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>18,21; 28,45</t>
+          <t>17,56; 28,19</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>7,44; 22,05</t>
+          <t>7,71; 22,89</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>29,79; 35,16</t>
+          <t>29,95; 35,34</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>28,36; 34,34</t>
+          <t>28,78; 34,29</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>29,95; 36,06</t>
+          <t>30,21; 36,2</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>14,91; 20,34</t>
+          <t>14,83; 20,22</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>26,08; 30,73</t>
+          <t>26,44; 30,93</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>26,95; 31,71</t>
+          <t>26,88; 32,04</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>28,21; 33,58</t>
+          <t>28,24; 33,18</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>14,02; 19,4</t>
+          <t>14,09; 19,48</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>16,86; 19,62</t>
+          <t>16,79; 19,55</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>28,82; 32,2</t>
+          <t>28,96; 32,19</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>31,97; 35,23</t>
+          <t>31,84; 35,12</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>9,33; 13,49</t>
+          <t>9,24; 13,54</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>26,25; 29,33</t>
+          <t>26,22; 29,37</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>30,12; 33,36</t>
+          <t>29,8; 33,2</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>34,21; 37,58</t>
+          <t>34,22; 37,57</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>13,97; 22,09</t>
+          <t>13,99; 22,41</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>22,07; 24,08</t>
+          <t>22,03; 24,11</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>29,83; 32,22</t>
+          <t>29,95; 32,24</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>33,55; 35,83</t>
+          <t>33,59; 35,88</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>12,67; 17,73</t>
+          <t>12,64; 17,32</t>
         </is>
       </c>
     </row>
@@ -1669,7 +1669,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que llega a fin de mes con dificultad o mucha dificultad</t>
+          <t>Población que llega a fin de mes con dificultad o mucha dificultad (tasa de respuesta: 99,03%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1927,62 +1927,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>21502; 44317</t>
+          <t>21657; 44096</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>50017; 81837</t>
+          <t>49527; 80490</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>39514; 67902</t>
+          <t>40846; 69020</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>15850; 36156</t>
+          <t>15952; 36474</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>29343; 54243</t>
+          <t>29341; 52880</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>33192; 60937</t>
+          <t>33389; 60995</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>35061; 58949</t>
+          <t>33980; 58758</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>9967; 23654</t>
+          <t>9825; 23006</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>56314; 90055</t>
+          <t>57306; 89798</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>89076; 133907</t>
+          <t>91600; 133068</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>80630; 118755</t>
+          <t>81603; 116992</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>28380; 52614</t>
+          <t>29494; 52579</t>
         </is>
       </c>
     </row>
@@ -2135,62 +2135,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>34402; 59833</t>
+          <t>33763; 60889</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>43743; 73300</t>
+          <t>44349; 73376</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>68188; 100676</t>
+          <t>67579; 101489</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>10521; 26194</t>
+          <t>9799; 26821</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>57173; 86295</t>
+          <t>56976; 87275</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>45121; 74990</t>
+          <t>44090; 72171</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>77086; 113880</t>
+          <t>77433; 114346</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>17370; 34422</t>
+          <t>17337; 34103</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>97945; 137213</t>
+          <t>95824; 136812</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>96328; 137607</t>
+          <t>96073; 138804</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>154166; 201738</t>
+          <t>153960; 200833</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>32215; 56743</t>
+          <t>30610; 54666</t>
         </is>
       </c>
     </row>
@@ -2343,62 +2343,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>64530; 96531</t>
+          <t>65210; 97420</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>190239; 241384</t>
+          <t>189994; 238100</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>171017; 214188</t>
+          <t>171230; 214180</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>19845; 93590</t>
+          <t>21259; 94388</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>25962; 47749</t>
+          <t>25735; 46881</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>60792; 90040</t>
+          <t>60307; 90726</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>42305; 67242</t>
+          <t>42616; 66846</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>13615; 26774</t>
+          <t>13952; 26605</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>96460; 134651</t>
+          <t>98272; 136905</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>259307; 316715</t>
+          <t>260323; 317915</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>224036; 278975</t>
+          <t>222209; 275099</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>32951; 114826</t>
+          <t>32039; 110772</t>
         </is>
       </c>
     </row>
@@ -2551,62 +2551,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>247502; 306005</t>
+          <t>246099; 304639</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>409119; 477998</t>
+          <t>409413; 477579</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>408151; 476799</t>
+          <t>404347; 472699</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>132629; 187644</t>
+          <t>131912; 186070</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>153065; 201800</t>
+          <t>154726; 201114</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>250821; 308096</t>
+          <t>250000; 307187</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>289647; 346558</t>
+          <t>290021; 345007</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>65027; 159359</t>
+          <t>64007; 159376</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>416065; 488824</t>
+          <t>416157; 489573</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>680450; 766858</t>
+          <t>679871; 766287</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>713166; 802223</t>
+          <t>711422; 800983</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>180461; 319641</t>
+          <t>186128; 321282</t>
         </is>
       </c>
     </row>
@@ -2759,62 +2759,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>100674; 134638</t>
+          <t>99183; 135090</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>188753; 234232</t>
+          <t>188294; 233146</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>264887; 318513</t>
+          <t>269350; 317456</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>98789; 136736</t>
+          <t>97665; 136005</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>173939; 218070</t>
+          <t>171531; 217591</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>285688; 343319</t>
+          <t>285620; 342706</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>365767; 420547</t>
+          <t>368008; 422095</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>223253; 432141</t>
+          <t>223549; 420355</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>284939; 344228</t>
+          <t>282887; 342907</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>489540; 559672</t>
+          <t>487187; 561128</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>647073; 722348</t>
+          <t>648051; 723841</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>335993; 571267</t>
+          <t>336154; 544307</t>
         </is>
       </c>
     </row>
@@ -2967,62 +2967,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>24607; 47178</t>
+          <t>24423; 45497</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>41746; 68864</t>
+          <t>42139; 66466</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>51830; 80990</t>
+          <t>49992; 80240</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>16509; 48936</t>
+          <t>17114; 50793</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>367682; 433972</t>
+          <t>369742; 436227</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>312699; 378704</t>
+          <t>317391; 378127</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>321947; 387579</t>
+          <t>324739; 389136</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>111567; 152194</t>
+          <t>110919; 151266</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>398560; 469617</t>
+          <t>403962; 472641</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>368379; 433309</t>
+          <t>367311; 437820</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>383577; 456497</t>
+          <t>383879; 451080</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>136020; 188200</t>
+          <t>136672; 189004</t>
         </is>
       </c>
     </row>
@@ -3175,62 +3175,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>543525; 632497</t>
+          <t>541533; 630352</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>981170; 1096333</t>
+          <t>985918; 1095882</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>1073694; 1183343</t>
+          <t>1069232; 1179698</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>311316; 450132</t>
+          <t>308212; 451790</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>869961; 972030</t>
+          <t>869008; 973268</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>1064710; 1179254</t>
+          <t>1053235; 1173454</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>1202114; 1320582</t>
+          <t>1202382; 1320028</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>491141; 776631</t>
+          <t>491675; 787592</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>1443011; 1574333</t>
+          <t>1440346; 1576261</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>2069623; 2235419</t>
+          <t>2078477; 2237138</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>2305511; 2462635</t>
+          <t>2308755; 2465560</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>868009; 1215053</t>
+          <t>866071; 1186683</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P71_R-Clase-trans_dic.xlsx
+++ b/data/trans_dic/P71_R-Clase-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>4,85%</t>
+          <t>5,25%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>3,39%</t>
+          <t>3,76%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>4,16%</t>
+          <t>4,55%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>4,63; 9,42</t>
+          <t>4,57; 9,62</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>11,41; 18,55</t>
+          <t>11,52; 18,78</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>9,62; 16,26</t>
+          <t>9,22; 16,03</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>3,17; 7,25</t>
+          <t>3,46; 7,83</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>9,7; 17,48</t>
+          <t>9,75; 18,2</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>10,65; 19,46</t>
+          <t>10,42; 19,11</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>9,79; 16,93</t>
+          <t>9,93; 17,07</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>2,21; 5,17</t>
+          <t>2,49; 5,48</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>7,44; 11,66</t>
+          <t>7,1; 11,55</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>12,25; 17,8</t>
+          <t>11,93; 17,53</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>10,58; 15,17</t>
+          <t>10,36; 15,15</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>3,11; 5,54</t>
+          <t>3,32; 5,86</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>3,76%</t>
+          <t>3,71%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>6,51%</t>
+          <t>6,71%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>5,02%</t>
+          <t>5,11%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>9,35; 16,86</t>
+          <t>9,57; 16,39</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>10,72; 17,74</t>
+          <t>10,6; 17,67</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>18,0; 27,03</t>
+          <t>18,31; 27,27</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>2,17; 5,95</t>
+          <t>2,29; 5,89</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>15,56; 23,84</t>
+          <t>15,27; 23,7</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>13,08; 21,41</t>
+          <t>13,27; 21,79</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>20,89; 30,85</t>
+          <t>21,15; 30,0</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>4,55; 8,96</t>
+          <t>4,72; 8,94</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>13,17; 18,81</t>
+          <t>13,24; 18,93</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>12,8; 18,49</t>
+          <t>12,7; 18,56</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>20,64; 26,92</t>
+          <t>20,56; 27,2</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>3,68; 6,57</t>
+          <t>3,84; 6,41</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>8,35%</t>
+          <t>13,46%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>11,68%</t>
+          <t>12,01%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>9,01%</t>
+          <t>13,05%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>12,22; 18,26</t>
+          <t>11,94; 17,93</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>30,23; 37,89</t>
+          <t>30,1; 38,1</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>33,07; 41,36</t>
+          <t>32,84; 41,98</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>3,19; 14,14</t>
+          <t>10,37; 17,16</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>15,61; 28,44</t>
+          <t>16,03; 28,32</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>23,35; 35,13</t>
+          <t>22,99; 34,79</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>26,12; 40,97</t>
+          <t>26,15; 41,78</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>8,42; 16,05</t>
+          <t>8,33; 16,3</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>14,07; 19,6</t>
+          <t>13,76; 19,38</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>29,36; 35,86</t>
+          <t>29,44; 35,72</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>32,63; 40,4</t>
+          <t>32,81; 39,94</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>3,85; 13,29</t>
+          <t>10,47; 15,63</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>15,23%</t>
+          <t>15,58%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>12,4%</t>
+          <t>16,55%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>13,85%</t>
+          <t>16,0%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>20,14; 24,93</t>
+          <t>20,24; 24,97</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>35,49; 41,4</t>
+          <t>35,48; 41,37</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>35,42; 41,41</t>
+          <t>35,83; 41,39</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>12,87; 18,15</t>
+          <t>13,32; 18,09</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>22,34; 29,04</t>
+          <t>22,34; 29,03</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>32,69; 40,17</t>
+          <t>32,98; 40,18</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>35,33; 42,03</t>
+          <t>35,23; 41,71</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>6,58; 16,39</t>
+          <t>14,62; 19,05</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>21,74; 25,57</t>
+          <t>21,74; 25,55</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>35,44; 39,95</t>
+          <t>35,38; 39,88</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>36,25; 40,82</t>
+          <t>36,29; 40,77</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>9,32; 16,09</t>
+          <t>14,43; 17,82</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>24,67%</t>
+          <t>29,34%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>34,95%</t>
+          <t>29,8%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>31,16%</t>
+          <t>29,61%</t>
         </is>
       </c>
     </row>
@@ -1277,69 +1277,69 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>28,63; 39,0</t>
+          <t>28,83; 38,86</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>36,88; 45,66</t>
+          <t>36,96; 45,63</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>43,8; 51,63</t>
+          <t>43,22; 51,29</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>20,85; 29,03</t>
+          <t>25,45; 33,44</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>30,99; 39,31</t>
+          <t>31,88; 40,11</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>37,66; 45,19</t>
+          <t>37,67; 45,12</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>49,91; 57,25</t>
+          <t>49,71; 56,82</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>27,84; 52,35</t>
+          <t>27,22; 32,9</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>31,44; 38,1</t>
+          <t>31,69; 38,2</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>38,39; 44,22</t>
+          <t>38,6; 44,06</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>47,93; 53,53</t>
+          <t>47,78; 53,07</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>26,44; 42,81</t>
+          <t>27,32; 32,14</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1364,7 +1364,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>13,54%</t>
+          <t>15,92%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>17,43%</t>
+          <t>17,98%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>16,54%</t>
+          <t>17,55%</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>8,32; 15,5</t>
+          <t>8,49; 15,85</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>15,96; 25,18</t>
+          <t>15,91; 25,67</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>17,56; 28,19</t>
+          <t>17,79; 27,73</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>7,71; 22,89</t>
+          <t>9,33; 25,38</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>29,95; 35,34</t>
+          <t>30,17; 35,53</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>28,78; 34,29</t>
+          <t>28,52; 34,31</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>30,21; 36,2</t>
+          <t>30,11; 35,95</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>14,83; 20,22</t>
+          <t>15,15; 20,71</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>26,44; 30,93</t>
+          <t>26,33; 30,93</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>26,88; 32,04</t>
+          <t>26,79; 31,82</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>28,24; 33,18</t>
+          <t>28,42; 33,53</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>14,09; 19,48</t>
+          <t>15,07; 20,49</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>11,95%</t>
+          <t>14,21%</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>14,44%</t>
+          <t>15,55%</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>16,79; 19,55</t>
+          <t>16,69; 19,47</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>28,96; 32,19</t>
+          <t>29,06; 32,11</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>31,84; 35,12</t>
+          <t>31,98; 35,35</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>9,24; 13,54</t>
+          <t>12,89; 15,58</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>26,22; 29,37</t>
+          <t>26,35; 29,49</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>29,8; 33,2</t>
+          <t>29,77; 33,17</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>34,22; 37,57</t>
+          <t>34,15; 37,37</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>13,99; 22,41</t>
+          <t>15,67; 17,89</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>22,03; 24,11</t>
+          <t>22,01; 24,08</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>29,95; 32,24</t>
+          <t>29,87; 32,23</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>33,59; 35,88</t>
+          <t>33,56; 35,87</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>12,64; 17,32</t>
+          <t>14,69; 16,48</t>
         </is>
       </c>
     </row>
@@ -1874,7 +1874,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>24411</t>
+          <t>28814</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>15073</t>
+          <t>18296</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1914,7 +1914,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>39485</t>
+          <t>47110</t>
         </is>
       </c>
     </row>
@@ -1927,62 +1927,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>21657; 44096</t>
+          <t>21369; 45013</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>49527; 80490</t>
+          <t>50016; 81508</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>40846; 69020</t>
+          <t>39109; 68014</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>15952; 36474</t>
+          <t>19001; 42970</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>29341; 52880</t>
+          <t>29491; 55070</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>33389; 60995</t>
+          <t>32665; 59902</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>33980; 58758</t>
+          <t>34469; 59252</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>9825; 23006</t>
+          <t>12114; 26615</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>57306; 89798</t>
+          <t>54738; 89021</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>91600; 133068</t>
+          <t>89155; 131029</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>81603; 116992</t>
+          <t>79902; 116848</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>29494; 52579</t>
+          <t>34334; 60588</t>
         </is>
       </c>
     </row>
@@ -2082,7 +2082,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>16976</t>
+          <t>17906</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2102,7 +2102,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>24792</t>
+          <t>28242</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -2122,7 +2122,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>41768</t>
+          <t>46147</t>
         </is>
       </c>
     </row>
@@ -2135,62 +2135,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>33763; 60889</t>
+          <t>34556; 59198</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>44349; 73376</t>
+          <t>43835; 73095</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>67579; 101489</t>
+          <t>68729; 102384</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>9799; 26821</t>
+          <t>11032; 28376</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>56976; 87275</t>
+          <t>55905; 86761</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>44090; 72171</t>
+          <t>44721; 73462</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>77433; 114346</t>
+          <t>78407; 111199</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>17337; 34103</t>
+          <t>19837; 37603</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>95824; 136812</t>
+          <t>96282; 137651</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>96073; 138804</t>
+          <t>95335; 139380</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>153960; 200833</t>
+          <t>153403; 202895</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>30610; 54666</t>
+          <t>34626; 57825</t>
         </is>
       </c>
     </row>
@@ -2290,7 +2290,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>55704</t>
+          <t>63353</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2310,7 +2310,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>19364</t>
+          <t>22385</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2330,7 +2330,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>75068</t>
+          <t>85738</t>
         </is>
       </c>
     </row>
@@ -2343,62 +2343,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>65210; 97420</t>
+          <t>63698; 95684</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>189994; 238100</t>
+          <t>189142; 239431</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>171230; 214180</t>
+          <t>170027; 217356</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>21259; 94388</t>
+          <t>48785; 80752</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>25735; 46881</t>
+          <t>26419; 46693</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>60307; 90726</t>
+          <t>59387; 89842</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>42616; 66846</t>
+          <t>42663; 68166</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>13952; 26605</t>
+          <t>15527; 30372</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>98272; 136905</t>
+          <t>96141; 135374</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>260323; 317915</t>
+          <t>261050; 316721</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>222209; 275099</t>
+          <t>223414; 271955</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>32039; 110772</t>
+          <t>68757; 102656</t>
         </is>
       </c>
     </row>
@@ -2498,7 +2498,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>156060</t>
+          <t>174480</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2518,7 +2518,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>120561</t>
+          <t>141586</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2538,7 +2538,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>276622</t>
+          <t>316065</t>
         </is>
       </c>
     </row>
@@ -2551,62 +2551,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>246099; 304639</t>
+          <t>247312; 305111</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>409413; 477579</t>
+          <t>409291; 477180</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>404347; 472699</t>
+          <t>408991; 472476</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>131912; 186070</t>
+          <t>149128; 202617</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>154726; 201114</t>
+          <t>154694; 200991</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>250000; 307187</t>
+          <t>252244; 307249</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>290021; 345007</t>
+          <t>289151; 342410</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>64007; 159376</t>
+          <t>125027; 162980</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>416157; 489573</t>
+          <t>416178; 489190</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>679871; 766287</t>
+          <t>678723; 765093</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>711422; 800983</t>
+          <t>712167; 800142</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>186128; 321282</t>
+          <t>285049; 352108</t>
         </is>
       </c>
     </row>
@@ -2706,7 +2706,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>115554</t>
+          <t>162903</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>280608</t>
+          <t>246232</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2746,7 +2746,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>396162</t>
+          <t>409135</t>
         </is>
       </c>
     </row>
@@ -2759,69 +2759,69 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>99183; 135090</t>
+          <t>99850; 134610</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>188294; 233146</t>
+          <t>188704; 232984</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>269350; 317456</t>
+          <t>265762; 315368</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>97665; 136005</t>
+          <t>141322; 185671</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>171531; 217591</t>
+          <t>176477; 222032</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>285620; 342706</t>
+          <t>285675; 342211</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>368008; 422095</t>
+          <t>366528; 418926</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>223549; 420355</t>
+          <t>224923; 271909</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>282887; 342907</t>
+          <t>285183; 343790</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>487187; 561128</t>
+          <t>489764; 559050</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>648051; 723841</t>
+          <t>646146; 717627</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>336154; 544307</t>
+          <t>377450; 444009</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -2914,7 +2914,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>30037</t>
+          <t>35111</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2934,7 +2934,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>130374</t>
+          <t>149176</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -2954,7 +2954,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>160411</t>
+          <t>184286</t>
         </is>
       </c>
     </row>
@@ -2967,62 +2967,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>24423; 45497</t>
+          <t>24926; 46533</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>42139; 66466</t>
+          <t>42005; 67755</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>49992; 80240</t>
+          <t>50637; 78929</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>17114; 50793</t>
+          <t>20575; 55974</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>369742; 436227</t>
+          <t>372366; 438548</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>317391; 378127</t>
+          <t>314530; 378276</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>324739; 389136</t>
+          <t>323664; 386447</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>110919; 151266</t>
+          <t>125694; 171793</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>403962; 472641</t>
+          <t>402251; 472578</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>367311; 437820</t>
+          <t>366130; 434822</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>383879; 451080</t>
+          <t>386426; 455848</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>136672; 189004</t>
+          <t>158262; 215178</t>
         </is>
       </c>
     </row>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>398742</t>
+          <t>482566</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -3142,7 +3142,7 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>590773</t>
+          <t>605917</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3162,7 +3162,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>989515</t>
+          <t>1088483</t>
         </is>
       </c>
     </row>
@@ -3175,62 +3175,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>541533; 630352</t>
+          <t>538069; 627911</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>985918; 1095882</t>
+          <t>989142; 1093214</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>1069232; 1179698</t>
+          <t>1074034; 1187306</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>308212; 451790</t>
+          <t>437814; 529411</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>869008; 973268</t>
+          <t>873087; 977322</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>1053235; 1173454</t>
+          <t>1052200; 1172455</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>1202382; 1320028</t>
+          <t>1199939; 1312978</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>491675; 787592</t>
+          <t>564813; 644657</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>1440346; 1576261</t>
+          <t>1438974; 1574629</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>2078477; 2237138</t>
+          <t>2072517; 2236155</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>2308755; 2465560</t>
+          <t>2306260; 2465112</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>866071; 1186683</t>
+          <t>1028469; 1153532</t>
         </is>
       </c>
     </row>
